--- a/datadog_monitoring.xlsx
+++ b/datadog_monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/meta_ai_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D3C7DF-92A3-7248-AC46-088C23EA6EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA12FC3A-DBCE-C741-AD21-8C12648E792D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>task_name</t>
   </si>
@@ -257,6 +257,14 @@
     5. **권장 사항(Recommendations)** — 엔지니어링 팀을 위한 실행 가능한 향후 단계
     6. **부록(Appendix)** — 관련된 경우 원본 오류 샘플  
 보고서는 {output_path} 이름으로 저장합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>task_output_file</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{output_path}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -753,21 +761,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965F465-69CB-8643-BA15-521BEF7BAC6E}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="102" customWidth="1"/>
-    <col min="3" max="3" width="45.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="38.28515625" customWidth="1"/>
-    <col min="9" max="10" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="74.28515625" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="9" max="9" width="38.28515625" customWidth="1"/>
+    <col min="10" max="11" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -778,28 +787,31 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="I1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="199" customHeight="1">
+    <row r="2" spans="1:11" ht="199" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,25 +821,26 @@
       <c r="C2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="164" customHeight="1">
+    <row r="3" spans="1:11" ht="164" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -837,25 +850,26 @@
       <c r="C3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="9"/>
       <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="203" customHeight="1">
+    <row r="4" spans="1:11" ht="203" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -865,25 +879,28 @@
       <c r="C4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="4"/>
       <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:10" ht="139" customHeight="1">
+    <row r="5" spans="1:11" ht="139" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -893,23 +910,24 @@
       <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="11"/>
       <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/datadog_monitoring.xlsx
+++ b/datadog_monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jck/WORK/DEV/meta_ai_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA12FC3A-DBCE-C741-AD21-8C12648E792D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0EBCB7-6E7C-D74E-AE76-8802F726DF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1B6F41E7-F757-EF41-AEAE-051A461303B9}"/>
   </bookViews>
@@ -765,13 +765,13 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="74.28515625" customWidth="1"/>
-    <col min="3" max="3" width="31.5703125" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="74.28515625" customWidth="1"/>
+    <col min="4" max="4" width="31.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" customWidth="1"/>
     <col min="9" max="9" width="38.28515625" customWidth="1"/>
     <col min="10" max="11" width="19.28515625" customWidth="1"/>
   </cols>
@@ -781,19 +781,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>3</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>8</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>34</v>
@@ -815,17 +815,17 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
@@ -844,18 +844,18 @@
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8" t="s">
         <v>7</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>9</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>17</v>
@@ -873,20 +873,20 @@
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -904,18 +904,18 @@
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6"/>
+      <c r="F5" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>10</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>23</v>
